--- a/data/Jul_2026.xlsx
+++ b/data/Jul_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Dropbox\ZYN_ELECTRICAL\Reportings\MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B17CB5F-FEC2-4F30-AF72-BF27C9E70DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE87B6F0-07FB-4AB3-929C-2DD9B5E4FEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" tabRatio="852" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="852" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PowerHouse Data" sheetId="2" r:id="rId1"/>
@@ -3202,7 +3202,9 @@
       <c r="L2" s="25">
         <v>1702</v>
       </c>
-      <c r="M2" s="25"/>
+      <c r="M2" s="25">
+        <v>1702</v>
+      </c>
       <c r="N2" s="25"/>
       <c r="O2" s="25"/>
       <c r="P2" s="25"/>
@@ -3259,7 +3261,9 @@
       <c r="L3" s="24">
         <v>24103700</v>
       </c>
-      <c r="M3" s="24"/>
+      <c r="M3" s="24">
+        <v>24112250</v>
+      </c>
       <c r="N3" s="24"/>
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
@@ -3316,7 +3320,9 @@
       <c r="L4" s="24">
         <v>3788</v>
       </c>
-      <c r="M4" s="24"/>
+      <c r="M4" s="24">
+        <v>3812</v>
+      </c>
       <c r="N4" s="24"/>
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
@@ -3373,7 +3379,9 @@
       <c r="L5" s="24">
         <v>6521</v>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="24">
+        <v>6545</v>
+      </c>
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
@@ -3430,7 +3438,9 @@
       <c r="L6" s="24">
         <v>688</v>
       </c>
-      <c r="M6" s="24"/>
+      <c r="M6" s="24">
+        <v>688</v>
+      </c>
       <c r="N6" s="24"/>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
@@ -3487,7 +3497,9 @@
       <c r="L7" s="24">
         <v>25850</v>
       </c>
-      <c r="M7" s="24"/>
+      <c r="M7" s="24">
+        <v>25850</v>
+      </c>
       <c r="N7" s="24"/>
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
@@ -3544,7 +3556,9 @@
       <c r="L8" s="24">
         <v>5645</v>
       </c>
-      <c r="M8" s="24"/>
+      <c r="M8" s="24">
+        <v>5645</v>
+      </c>
       <c r="N8" s="24"/>
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
@@ -3601,7 +3615,9 @@
       <c r="L9" s="24">
         <v>12503.8</v>
       </c>
-      <c r="M9" s="24"/>
+      <c r="M9" s="24">
+        <v>12503.8</v>
+      </c>
       <c r="N9" s="24"/>
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
@@ -3658,7 +3674,9 @@
       <c r="L10" s="24">
         <v>3287205</v>
       </c>
-      <c r="M10" s="24"/>
+      <c r="M10" s="24">
+        <v>3299866</v>
+      </c>
       <c r="N10" s="24"/>
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
@@ -3715,7 +3733,9 @@
       <c r="L11" s="24">
         <v>342023</v>
       </c>
-      <c r="M11" s="24"/>
+      <c r="M11" s="24">
+        <v>344378</v>
+      </c>
       <c r="N11" s="24"/>
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
@@ -3772,7 +3792,9 @@
       <c r="L12" s="24">
         <v>0</v>
       </c>
-      <c r="M12" s="24"/>
+      <c r="M12" s="24">
+        <v>0</v>
+      </c>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
@@ -3830,7 +3852,9 @@
       <c r="L13" s="24">
         <v>0</v>
       </c>
-      <c r="M13" s="24"/>
+      <c r="M13" s="24">
+        <v>85</v>
+      </c>
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
@@ -3889,7 +3913,10 @@
         <f>K14</f>
         <v>5134</v>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="24">
+        <f>L14-M13</f>
+        <v>5049</v>
+      </c>
       <c r="N14" s="24"/>
       <c r="O14" s="24"/>
       <c r="P14" s="24"/>
@@ -3923,6 +3950,9 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="L14" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4200,8 +4230,8 @@
         <v>5184</v>
       </c>
       <c r="X3" s="12">
-        <f>Diesel!I4</f>
-        <v>38844</v>
+        <f>Diesel!I3</f>
+        <v>38923</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
@@ -4283,8 +4313,8 @@
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
       <c r="X4" s="12">
-        <f>Diesel!I5</f>
-        <v>37229</v>
+        <f>Diesel!I4</f>
+        <v>38844</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
@@ -4366,7 +4396,7 @@
       <c r="V5" s="12"/>
       <c r="W5" s="12"/>
       <c r="X5" s="12">
-        <f>Diesel!I6</f>
+        <f>Diesel!I5</f>
         <v>37229</v>
       </c>
     </row>
@@ -4449,8 +4479,8 @@
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
       <c r="X6" s="12">
-        <f>Diesel!I7</f>
-        <v>36367.5</v>
+        <f>Diesel!I6</f>
+        <v>37229</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
@@ -4532,7 +4562,7 @@
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
       <c r="X7" s="12">
-        <f>Diesel!I8</f>
+        <f>Diesel!I7</f>
         <v>36367.5</v>
       </c>
     </row>
@@ -4615,8 +4645,8 @@
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="12">
-        <f>Diesel!I9</f>
-        <v>35373</v>
+        <f>Diesel!I8</f>
+        <v>36367.5</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
@@ -4698,8 +4728,8 @@
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
       <c r="X9" s="12">
-        <f>Diesel!I10</f>
-        <v>35323</v>
+        <f>Diesel!I9</f>
+        <v>35373</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
@@ -4781,7 +4811,7 @@
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
       <c r="X10" s="12">
-        <f>Diesel!I11</f>
+        <f>Diesel!I10</f>
         <v>35323</v>
       </c>
     </row>
@@ -4864,8 +4894,8 @@
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
       <c r="X11" s="12">
-        <f>Diesel!I12</f>
-        <v>0</v>
+        <f>Diesel!I11</f>
+        <v>35323</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
@@ -4875,69 +4905,69 @@
       <c r="B12" s="20">
         <f>Table113456[[#This Row],[Main Tank
 Consumption (Liters)]]</f>
-        <v>30189</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5">
         <f>Table1135[[#This Row],[NEPA Consumption (KWH)]]</f>
-        <v>-24103700</v>
+        <v>8550</v>
       </c>
       <c r="D12" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
 Run Hours]]</f>
-        <v>-3788</v>
+        <v>24</v>
       </c>
       <c r="E12" s="10">
         <f>Table113[[#This Row],[Comp E75 -2
 Run Hours]]</f>
-        <v>-6521</v>
+        <v>24</v>
       </c>
       <c r="F12" s="10">
         <f>Table113[[#This Row],[Comp E75 -3
 Run Hours]]</f>
-        <v>-688</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10">
         <f>Table113[[#This Row],[Comp E55 Run Hours]]</f>
-        <v>-25850</v>
+        <v>0</v>
       </c>
       <c r="H12" s="13">
         <f>Table113456[[#This Row],[DG Milling Run Hours]]</f>
-        <v>-5645</v>
+        <v>0</v>
       </c>
       <c r="I12" s="12">
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hours]]</f>
-        <v>-12503.8</v>
+        <v>0</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="12">
         <f>Table113[[#This Row],[Comp E75 -1
 Rem Hours To Service]]</f>
-        <v>5440</v>
+        <v>1628</v>
       </c>
       <c r="L12" s="12">
         <f>Table113[[#This Row],[Comp E75 -2
 Rem Hours To Service]]</f>
-        <v>8066</v>
+        <v>1521</v>
       </c>
       <c r="M12" s="12">
         <f>Table113[[#This Row],[Comp E75 -3
 Rem Hours To Service]]</f>
-        <v>4000</v>
+        <v>3312</v>
       </c>
       <c r="N12" s="12">
         <f>Table113[[#This Row],[Comp E55 Rem Hours To Service]]</f>
-        <v>26930</v>
+        <v>1080</v>
       </c>
       <c r="O12" s="12">
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hr Meter3]]</f>
-        <v>5824</v>
+        <v>179</v>
       </c>
       <c r="P12" s="12">
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hr Meter5]]</f>
-        <v>12643.5</v>
+        <v>139.70000000000073</v>
       </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
@@ -4947,8 +4977,8 @@
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
       <c r="X12" s="12">
-        <f>Diesel!I13</f>
-        <v>0</v>
+        <f>Diesel!I12</f>
+        <v>35238</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
@@ -4958,39 +4988,39 @@
       <c r="B13" s="20">
         <f>Table113456[[#This Row],[Main Tank
 Consumption (Liters)]]</f>
-        <v>0</v>
+        <v>30189</v>
       </c>
       <c r="C13" s="5">
         <f>Table1135[[#This Row],[NEPA Consumption (KWH)]]</f>
-        <v>0</v>
+        <v>-24112250</v>
       </c>
       <c r="D13" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
 Run Hours]]</f>
-        <v>0</v>
+        <v>-3812</v>
       </c>
       <c r="E13" s="10">
         <f>Table113[[#This Row],[Comp E75 -2
 Run Hours]]</f>
-        <v>0</v>
+        <v>-6545</v>
       </c>
       <c r="F13" s="10">
         <f>Table113[[#This Row],[Comp E75 -3
 Run Hours]]</f>
-        <v>0</v>
+        <v>-688</v>
       </c>
       <c r="G13" s="10">
         <f>Table113[[#This Row],[Comp E55 Run Hours]]</f>
-        <v>0</v>
+        <v>-25850</v>
       </c>
       <c r="H13" s="13">
         <f>Table113456[[#This Row],[DG Milling Run Hours]]</f>
-        <v>0</v>
+        <v>-5645</v>
       </c>
       <c r="I13" s="12">
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hours]]</f>
-        <v>0</v>
+        <v>-12503.8</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="12">
@@ -5030,7 +5060,7 @@
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12">
-        <f>Diesel!I14</f>
+        <f>Diesel!I13</f>
         <v>0</v>
       </c>
     </row>
@@ -5113,7 +5143,7 @@
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12">
-        <f>Diesel!I15</f>
+        <f>Diesel!I14</f>
         <v>0</v>
       </c>
     </row>
@@ -5196,7 +5226,7 @@
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
       <c r="X15" s="12">
-        <f>Diesel!I16</f>
+        <f>Diesel!I15</f>
         <v>0</v>
       </c>
     </row>
@@ -5279,7 +5309,7 @@
       <c r="V16" s="12"/>
       <c r="W16" s="12"/>
       <c r="X16" s="12">
-        <f>Diesel!I17</f>
+        <f>Diesel!I16</f>
         <v>0</v>
       </c>
     </row>
@@ -5362,7 +5392,7 @@
       <c r="V17" s="12"/>
       <c r="W17" s="12"/>
       <c r="X17" s="12">
-        <f>Diesel!I18</f>
+        <f>Diesel!I17</f>
         <v>0</v>
       </c>
     </row>
@@ -5445,7 +5475,7 @@
       <c r="V18" s="12"/>
       <c r="W18" s="12"/>
       <c r="X18" s="12">
-        <f>Diesel!I19</f>
+        <f>Diesel!I18</f>
         <v>0</v>
       </c>
     </row>
@@ -5528,7 +5558,7 @@
       <c r="V19" s="12"/>
       <c r="W19" s="12"/>
       <c r="X19" s="12">
-        <f>Diesel!I20</f>
+        <f>Diesel!I19</f>
         <v>0</v>
       </c>
     </row>
@@ -5611,7 +5641,7 @@
       <c r="V20" s="12"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12">
-        <f>Diesel!I21</f>
+        <f>Diesel!I20</f>
         <v>0</v>
       </c>
     </row>
@@ -5694,7 +5724,7 @@
       <c r="V21" s="12"/>
       <c r="W21" s="12"/>
       <c r="X21" s="12">
-        <f>Diesel!I22</f>
+        <f>Diesel!I21</f>
         <v>0</v>
       </c>
     </row>
@@ -5777,7 +5807,7 @@
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12">
-        <f>Diesel!I23</f>
+        <f>Diesel!I22</f>
         <v>0</v>
       </c>
     </row>
@@ -5860,7 +5890,7 @@
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
       <c r="X23" s="12">
-        <f>Diesel!I24</f>
+        <f>Diesel!I23</f>
         <v>0</v>
       </c>
     </row>
@@ -5943,7 +5973,7 @@
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
       <c r="X24" s="12">
-        <f>Diesel!I25</f>
+        <f>Diesel!I24</f>
         <v>0</v>
       </c>
     </row>
@@ -6026,7 +6056,7 @@
       <c r="V25" s="12"/>
       <c r="W25" s="12"/>
       <c r="X25" s="12">
-        <f>Diesel!I26</f>
+        <f>Diesel!I25</f>
         <v>0</v>
       </c>
     </row>
@@ -6109,7 +6139,7 @@
       <c r="V26" s="12"/>
       <c r="W26" s="12"/>
       <c r="X26" s="12">
-        <f>Diesel!I27</f>
+        <f>Diesel!I26</f>
         <v>0</v>
       </c>
     </row>
@@ -6192,7 +6222,7 @@
       <c r="V27" s="12"/>
       <c r="W27" s="12"/>
       <c r="X27" s="12">
-        <f>Diesel!I28</f>
+        <f>Diesel!I27</f>
         <v>0</v>
       </c>
     </row>
@@ -6275,7 +6305,7 @@
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
       <c r="X28" s="12">
-        <f>Diesel!I29</f>
+        <f>Diesel!I28</f>
         <v>0</v>
       </c>
     </row>
@@ -6358,7 +6388,7 @@
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
       <c r="X29" s="12">
-        <f>Diesel!I30</f>
+        <f>Diesel!I29</f>
         <v>0</v>
       </c>
     </row>
@@ -6441,7 +6471,7 @@
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
       <c r="X30" s="12">
-        <f>Diesel!I31</f>
+        <f>Diesel!I30</f>
         <v>0</v>
       </c>
     </row>
@@ -6524,7 +6554,7 @@
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
       <c r="X31" s="12">
-        <f>Diesel!I32</f>
+        <f>Diesel!I31</f>
         <v>0</v>
       </c>
     </row>
@@ -6607,7 +6637,7 @@
       <c r="V32" s="12"/>
       <c r="W32" s="12"/>
       <c r="X32" s="12">
-        <f>Diesel!I33</f>
+        <f>Diesel!I32</f>
         <v>0</v>
       </c>
     </row>
@@ -6689,8 +6719,8 @@
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
-      <c r="X33" s="7">
-        <f>Diesel!I34</f>
+      <c r="X33" s="12">
+        <f>Diesel!I33</f>
         <v>0</v>
       </c>
     </row>
@@ -7513,56 +7543,56 @@
       <c r="B12" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
 Run Hr]]-C11</f>
-        <v>-3788</v>
+        <v>24</v>
       </c>
       <c r="C12" s="7">
         <f>'PowerHouse Data'!$M$4</f>
-        <v>0</v>
+        <v>3812</v>
       </c>
       <c r="D12" s="13">
         <f>$N$3-Table113[[#This Row],[Comp E75 -1
 Run Hr]]</f>
-        <v>5440</v>
+        <v>1628</v>
       </c>
       <c r="E12" s="5">
         <f>Table113[[#This Row],[Comp E75 -2
 Run Hr]]-F11</f>
-        <v>-6521</v>
+        <v>24</v>
       </c>
       <c r="F12" s="7">
         <f>'PowerHouse Data'!$M$5</f>
-        <v>0</v>
+        <v>6545</v>
       </c>
       <c r="G12" s="13">
         <f>$O$3-Table113[[#This Row],[Comp E75 -2
 Run Hr]]</f>
-        <v>8066</v>
+        <v>1521</v>
       </c>
       <c r="H12" s="5">
         <f>Table113[[#This Row],[Comp E75 -3
 Run Hr]]-I11</f>
-        <v>-688</v>
+        <v>0</v>
       </c>
       <c r="I12" s="7">
         <f>'PowerHouse Data'!$M$6</f>
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="J12" s="13">
         <f>$P$3-Table113[[#This Row],[Comp E75 -3
 Run Hr]]</f>
-        <v>4000</v>
+        <v>3312</v>
       </c>
       <c r="K12" s="5">
         <f>Table113[[#This Row],[Comp E55 Run Hr]]-L11</f>
-        <v>-25850</v>
+        <v>0</v>
       </c>
       <c r="L12" s="7">
         <f>'PowerHouse Data'!$M$7</f>
-        <v>0</v>
+        <v>25850</v>
       </c>
       <c r="M12" s="13">
         <f>$Q$3-Table113[[#This Row],[Comp E55 Run Hr]]</f>
-        <v>26930</v>
+        <v>1080</v>
       </c>
       <c r="N12" s="28"/>
       <c r="O12" s="28"/>
@@ -7576,7 +7606,7 @@
       <c r="B13" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
 Run Hr]]-C12</f>
-        <v>0</v>
+        <v>-3812</v>
       </c>
       <c r="C13" s="7">
         <f>'PowerHouse Data'!$N$4</f>
@@ -7590,7 +7620,7 @@
       <c r="E13" s="5">
         <f>Table113[[#This Row],[Comp E75 -2
 Run Hr]]-F12</f>
-        <v>0</v>
+        <v>-6545</v>
       </c>
       <c r="F13" s="7">
         <f>'PowerHouse Data'!$N$5</f>
@@ -7604,7 +7634,7 @@
       <c r="H13" s="5">
         <f>Table113[[#This Row],[Comp E75 -3
 Run Hr]]-I12</f>
-        <v>0</v>
+        <v>-688</v>
       </c>
       <c r="I13" s="7">
         <f>'PowerHouse Data'!$N$6</f>
@@ -7617,7 +7647,7 @@
       </c>
       <c r="K13" s="5">
         <f>Table113[[#This Row],[Comp E55 Run Hr]]-L12</f>
-        <v>0</v>
+        <v>-25850</v>
       </c>
       <c r="L13" s="7">
         <f>'PowerHouse Data'!$N$7</f>
@@ -9860,7 +9890,7 @@
       </c>
       <c r="D12" s="31">
         <f>'PowerHouse Data'!$M$2</f>
-        <v>0</v>
+        <v>1702</v>
       </c>
       <c r="E12" s="13">
         <f t="shared" si="0"/>
@@ -9874,33 +9904,33 @@
         <f>Table113456[[#This Row],[Main Tank
 Opening Stock (Liters)]]-Table113456[[#This Row],[Main Tank
 Closing Stock (Liters)]]+Table113456[[#This Row],[Received (Liters)]]</f>
-        <v>30189</v>
+        <v>0</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>30189</v>
       </c>
       <c r="I12" s="31">
         <f>Table113456[[#This Row],[Main Tank
 Closing Stock (Liters)]]+V12</f>
-        <v>0</v>
+        <v>35238</v>
       </c>
       <c r="J12" s="13">
         <f>Table113456[[#This Row],[DG Milling Run Hr Meter]]-K11</f>
-        <v>-5645</v>
+        <v>0</v>
       </c>
       <c r="K12" s="31">
         <f>'PowerHouse Data'!$M$8</f>
-        <v>0</v>
+        <v>5645</v>
       </c>
       <c r="L12" s="13">
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hr Meter]]-M11</f>
-        <v>-12503.8</v>
+        <v>0</v>
       </c>
       <c r="M12" s="31">
         <f>'PowerHouse Data'!$M$9</f>
-        <v>0</v>
+        <v>12503.8</v>
       </c>
       <c r="N12" s="13">
         <v>5824</v>
@@ -9908,7 +9938,7 @@
       <c r="O12" s="13">
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hr Meter2]]-Table113456[[#This Row],[DG Milling Run Hr Meter]]</f>
-        <v>5824</v>
+        <v>179</v>
       </c>
       <c r="P12" s="13">
         <v>12643.5</v>
@@ -9917,11 +9947,11 @@
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hr Meter4]]-Table113456[[#This Row],[DG Parboiling 
 Run Hr Meter]]</f>
-        <v>12643.5</v>
+        <v>139.70000000000073</v>
       </c>
       <c r="R12" s="31">
         <f>'PowerHouse Data'!$M$13</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S12" s="13"/>
       <c r="T12" s="30">
@@ -9932,7 +9962,7 @@
       </c>
       <c r="V12" s="40">
         <f>'PowerHouse Data'!$M$14</f>
-        <v>0</v>
+        <v>5049</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -9944,7 +9974,7 @@
       </c>
       <c r="C13" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1702</v>
       </c>
       <c r="D13" s="31">
         <f>'PowerHouse Data'!$N$2</f>
@@ -9952,7 +9982,7 @@
       </c>
       <c r="E13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30189</v>
       </c>
       <c r="F13" s="13">
         <f>'PowerHouse Data'!$N$12</f>
@@ -9962,7 +9992,7 @@
         <f>Table113456[[#This Row],[Main Tank
 Opening Stock (Liters)]]-Table113456[[#This Row],[Main Tank
 Closing Stock (Liters)]]+Table113456[[#This Row],[Received (Liters)]]</f>
-        <v>0</v>
+        <v>30189</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" si="1"/>
@@ -9975,7 +10005,7 @@
       </c>
       <c r="J13" s="13">
         <f>Table113456[[#This Row],[DG Milling Run Hr Meter]]-K12</f>
-        <v>0</v>
+        <v>-5645</v>
       </c>
       <c r="K13" s="31">
         <f>'PowerHouse Data'!$N$8</f>
@@ -9984,7 +10014,7 @@
       <c r="L13" s="13">
         <f>Table113456[[#This Row],[DG Parboiling 
 Run Hr Meter]]-M12</f>
-        <v>0</v>
+        <v>-12503.8</v>
       </c>
       <c r="M13" s="31">
         <f>'PowerHouse Data'!$N$9</f>
@@ -22993,35 +23023,35 @@
       </c>
       <c r="C12" s="5">
         <f>'PowerHouse Data'!$M$3</f>
-        <v>0</v>
+        <v>24112250</v>
       </c>
       <c r="D12" s="5">
         <f>Table1135[[#This Row],[NEPA FINAL]]-C11</f>
-        <v>-24103700</v>
+        <v>8550</v>
       </c>
       <c r="E12" s="5">
         <f>(Table1135[[#This Row],[MILLING]]-F11)+(Table1135[[#This Row],[UTILITY / PARBOILING]]-G11)</f>
-        <v>-3629228</v>
+        <v>15016</v>
       </c>
       <c r="F12" s="5">
         <f>'PowerHouse Data'!$M$10</f>
-        <v>0</v>
+        <v>3299866</v>
       </c>
       <c r="G12" s="5">
         <f>'PowerHouse Data'!$M$11</f>
-        <v>0</v>
+        <v>344378</v>
       </c>
       <c r="H12" s="5">
         <f>Table1135[[#This Row],[MILLING]]-F11</f>
-        <v>-3287205</v>
+        <v>12661</v>
       </c>
       <c r="I12" s="5">
         <f>Table1135[[#This Row],[UTILITY / PARBOILING]]-G11</f>
-        <v>-342023</v>
+        <v>2355</v>
       </c>
       <c r="J12" s="5">
         <f>Table1135[[#This Row],[MILLING + UTILITY / PARBOILING]]-Table1135[[#This Row],[NEPA Consumption (KWH)]]</f>
-        <v>20474472</v>
+        <v>6466</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -23037,11 +23067,11 @@
       </c>
       <c r="D13" s="5">
         <f>Table1135[[#This Row],[NEPA FINAL]]-C12</f>
-        <v>0</v>
+        <v>-24112250</v>
       </c>
       <c r="E13" s="5">
         <f>(Table1135[[#This Row],[MILLING]]-F12)+(Table1135[[#This Row],[UTILITY / PARBOILING]]-G12)</f>
-        <v>0</v>
+        <v>-3644244</v>
       </c>
       <c r="F13" s="5">
         <f>'PowerHouse Data'!$N$10</f>
@@ -23053,15 +23083,15 @@
       </c>
       <c r="H13" s="5">
         <f>Table1135[[#This Row],[MILLING]]-F12</f>
-        <v>0</v>
+        <v>-3299866</v>
       </c>
       <c r="I13" s="5">
         <f>Table1135[[#This Row],[UTILITY / PARBOILING]]-G12</f>
-        <v>0</v>
+        <v>-344378</v>
       </c>
       <c r="J13" s="5">
         <f>Table1135[[#This Row],[MILLING + UTILITY / PARBOILING]]-Table1135[[#This Row],[NEPA Consumption (KWH)]]</f>
-        <v>0</v>
+        <v>20468006</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/Jul_2026.xlsx
+++ b/data/Jul_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Dropbox\ZYN_ELECTRICAL\Reportings\MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE87B6F0-07FB-4AB3-929C-2DD9B5E4FEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1793C22-E2B8-460F-A43A-E06410BC86AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="852" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,7 +594,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -707,8 +707,20 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2614,7 +2626,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD9BBFA2-2F77-42BF-9473-EA00078A9849}" name="Table11" displayName="Table11" ref="A1:X33" totalsRowShown="0" headerRowDxfId="72" headerRowBorderDxfId="71" tableBorderDxfId="70" totalsRowBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD9BBFA2-2F77-42BF-9473-EA00078A9849}" name="Table11" displayName="Table11" ref="A1:X34" totalsRowShown="0" headerRowDxfId="72" headerRowBorderDxfId="71" tableBorderDxfId="70" totalsRowBorderDxfId="69">
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{3B419577-373D-4E9B-865D-26BC24BCC615}" name="Date" dataDxfId="68"/>
     <tableColumn id="2" xr3:uid="{5575268A-18B4-4AE2-9F00-36D1511A2E6D}" name="Diesel Consumption_x000a_(LTRS)" dataDxfId="67">
@@ -2686,7 +2698,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36A0B8F6-1D49-4ED9-A151-8BA053CCE2F1}" name="Table113" displayName="Table113" ref="A1:Q33" totalsRowShown="0" headerRowDxfId="45" headerRowBorderDxfId="44" tableBorderDxfId="43" totalsRowBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{36A0B8F6-1D49-4ED9-A151-8BA053CCE2F1}" name="Table113" displayName="Table113" ref="A1:Q34" totalsRowShown="0" headerRowDxfId="45" headerRowBorderDxfId="44" tableBorderDxfId="43" totalsRowBorderDxfId="42">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{BE1398C8-B50B-4A4B-BD0B-DED2C439368D}" name="Date" dataDxfId="41"/>
     <tableColumn id="10" xr3:uid="{7342E3C6-CA38-4E51-A5F6-1A10AF77FD68}" name="Comp E75 -1_x000a_Run Hours" dataDxfId="40"/>
@@ -2725,7 +2737,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D8662DC1-E94E-4583-A821-BCD636E17FBE}" name="Table113456" displayName="Table113456" ref="A1:S33" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D8662DC1-E94E-4583-A821-BCD636E17FBE}" name="Table113456" displayName="Table113456" ref="A1:S34" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{FFA0CAE9-6D4C-42A7-9ED1-9D3CC33D3A39}" name="Date" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{C302EA9C-DA8B-412B-AE71-A781D1B622CE}" name="TIME " dataDxfId="18"/>
@@ -4055,9 +4067,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B2" s="7" t="e">
         <f>[2]!Table113456[[#This Row],[Consumption (Liters)]]</f>
@@ -4130,16 +4142,12 @@
       <c r="T2" s="19"/>
       <c r="U2" s="32"/>
       <c r="V2" s="32"/>
-      <c r="W2" s="34">
-        <v>2434</v>
-      </c>
-      <c r="X2" s="42">
-        <v>2434</v>
-      </c>
+      <c r="W2" s="34"/>
+      <c r="X2" s="43"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4236,7 +4244,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4319,7 +4327,7 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B5" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4402,7 +4410,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="B6" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4485,7 +4493,7 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="B7" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4568,7 +4576,7 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B8" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4651,7 +4659,7 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B9" s="23">
         <f>Table113456[[#This Row],[Main Tank
@@ -4734,7 +4742,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B10" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4817,7 +4825,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B11" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4900,7 +4908,7 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B12" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -4983,7 +4991,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="B13" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5066,7 +5074,7 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>46215</v>
+        <v>46214</v>
       </c>
       <c r="B14" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5149,7 +5157,7 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>46216</v>
+        <v>46215</v>
       </c>
       <c r="B15" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5232,7 +5240,7 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B16" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5315,7 +5323,7 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B17" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5398,7 +5406,7 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B18" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5481,7 +5489,7 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B19" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5564,7 +5572,7 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>46221</v>
+        <v>46220</v>
       </c>
       <c r="B20" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5647,7 +5655,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>46222</v>
+        <v>46221</v>
       </c>
       <c r="B21" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5730,7 +5738,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>46223</v>
+        <v>46222</v>
       </c>
       <c r="B22" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5813,7 +5821,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B23" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5896,7 +5904,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B24" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -5979,7 +5987,7 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B25" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -6062,7 +6070,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B26" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -6145,7 +6153,7 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="B27" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -6228,7 +6236,7 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="B28" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -6311,7 +6319,7 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="B29" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -6394,7 +6402,7 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B30" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -6477,7 +6485,7 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B31" s="20">
         <f>Table113456[[#This Row],[Main Tank
@@ -6560,7 +6568,7 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B32" s="23">
         <f>Table113456[[#This Row],[Main Tank
@@ -6643,7 +6651,7 @@
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B33" s="23">
         <f>Table113456[[#This Row],[Main Tank
@@ -6725,7 +6733,87 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="X34" s="21"/>
+      <c r="A34" s="4">
+        <v>46234</v>
+      </c>
+      <c r="B34" s="44">
+        <f>Table113456[[#This Row],[Main Tank
+Consumption (Liters)]]</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="44" t="e">
+        <f>Table1135[[#This Row],[NEPA Consumption (KWH)]]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D34" s="5">
+        <f>Table113[[#This Row],[Comp E75 -1
+Run Hours]]</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="44">
+        <f>Table113[[#This Row],[Comp E75 -2
+Run Hours]]</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="46">
+        <f>Table113[[#This Row],[Comp E75 -3
+Run Hours]]</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="7">
+        <f>Table113[[#This Row],[Comp E55 Run Hours]]</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="20">
+        <f>Table113456[[#This Row],[DG Milling Run Hours]]</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="6">
+        <f>Table113456[[#This Row],[DG Parboiling 
+Run Hours]]</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="K34" s="42">
+        <f>Table113[[#This Row],[Comp E75 -1
+Rem Hours To Service]]</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="42">
+        <f>Table113[[#This Row],[Comp E75 -2
+Rem Hours To Service]]</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="12">
+        <f>Table113[[#This Row],[Comp E75 -3
+Rem Hours To Service]]</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="42">
+        <f>Table113[[#This Row],[Comp E55 Rem Hours To Service]]</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="42">
+        <f>Table113456[[#This Row],[DG Parboiling 
+Run Hr Meter3]]</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="42">
+        <f>Table113456[[#This Row],[DG Parboiling 
+Run Hr Meter5]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="42"/>
+      <c r="T34" s="42"/>
+      <c r="U34" s="42"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="42"/>
+      <c r="X34" s="42">
+        <f>Diesel!I35</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
@@ -6851,7 +6939,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F89DDD-2A14-4746-BC3C-C1533FBE8EDA}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
@@ -6919,9 +7007,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B2" s="10">
         <v>21</v>
@@ -6966,7 +7054,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="10">
         <f>'PowerHouse Data'!D4-'PowerHouse Data'!C4</f>
@@ -7034,7 +7122,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7097,7 +7185,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B5" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7160,7 +7248,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="B6" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7223,7 +7311,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="B7" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7286,7 +7374,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B8" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7349,7 +7437,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B9" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7412,7 +7500,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B10" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7475,7 +7563,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B11" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7538,7 +7626,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B12" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7601,7 +7689,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="B13" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7664,7 +7752,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>46215</v>
+        <v>46214</v>
       </c>
       <c r="B14" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7727,7 +7815,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>46216</v>
+        <v>46215</v>
       </c>
       <c r="B15" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7790,7 +7878,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B16" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7853,7 +7941,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B17" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7916,7 +8004,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B18" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -7979,7 +8067,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B19" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8042,7 +8130,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>46221</v>
+        <v>46220</v>
       </c>
       <c r="B20" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8105,7 +8193,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>46222</v>
+        <v>46221</v>
       </c>
       <c r="B21" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8168,7 +8256,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>46223</v>
+        <v>46222</v>
       </c>
       <c r="B22" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8231,7 +8319,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B23" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8294,7 +8382,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B24" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8357,7 +8445,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B25" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8420,7 +8508,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B26" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8483,7 +8571,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="B27" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8546,7 +8634,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="B28" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8609,7 +8697,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="B29" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8672,7 +8760,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B30" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8735,7 +8823,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B31" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8798,7 +8886,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B32" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8861,7 +8949,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B33" s="5">
         <f>Table113[[#This Row],[Comp E75 -1
@@ -8921,6 +9009,46 @@
       <c r="O33" s="28"/>
       <c r="P33" s="28"/>
       <c r="Q33" s="28"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>46234</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="31">
+        <f>$N$2-Table113[[#This Row],[Comp E75 -1
+Run Hr]]</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="31">
+        <f>$O$2-Table113[[#This Row],[Comp E75 -2
+Run Hr]]</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="44">
+        <f>Table113[[#This Row],[Comp E75 -2
+Run Hr]]-I33</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="45"/>
+      <c r="J34" s="13">
+        <f>$O$2-Table113[[#This Row],[Comp E75 -2
+Run Hr]]</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="31">
+        <f>$Q$2-Table113[[#This Row],[Comp E55 Run Hr]]</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="7"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -9026,7 +9154,7 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="17">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="5">
@@ -9087,7 +9215,7 @@
     </row>
     <row r="3" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="18">
         <v>0.29166666666666669</v>
@@ -9174,7 +9302,7 @@
     </row>
     <row r="4" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="18">
         <v>0.29166666666666669</v>
@@ -9262,7 +9390,7 @@
     </row>
     <row r="5" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B5" s="18">
         <v>0.29166666666666669</v>
@@ -9350,7 +9478,7 @@
     </row>
     <row r="6" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="B6" s="18">
         <v>0.29166666666666669</v>
@@ -9438,7 +9566,7 @@
     </row>
     <row r="7" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="B7" s="18">
         <v>0.29166666666666669</v>
@@ -9526,7 +9654,7 @@
     </row>
     <row r="8" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B8" s="18">
         <v>0.29166666666666669</v>
@@ -9614,7 +9742,7 @@
     </row>
     <row r="9" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B9" s="18">
         <v>0.29166666666666669</v>
@@ -9702,7 +9830,7 @@
     </row>
     <row r="10" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B10" s="18">
         <v>0.29166666666666669</v>
@@ -9790,7 +9918,7 @@
     </row>
     <row r="11" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B11" s="18">
         <v>0.29166666666666669</v>
@@ -9879,7 +10007,7 @@
     </row>
     <row r="12" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B12" s="18">
         <v>0.29166666666666669</v>
@@ -9967,7 +10095,7 @@
     </row>
     <row r="13" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="B13" s="18">
         <v>0.29166666666666669</v>
@@ -10055,7 +10183,7 @@
     </row>
     <row r="14" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17">
-        <v>46215</v>
+        <v>46214</v>
       </c>
       <c r="B14" s="18">
         <v>0.29166666666666669</v>
@@ -10143,7 +10271,7 @@
     </row>
     <row r="15" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17">
-        <v>46216</v>
+        <v>46215</v>
       </c>
       <c r="B15" s="18">
         <v>0.29166666666666669</v>
@@ -10231,7 +10359,7 @@
     </row>
     <row r="16" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B16" s="18">
         <v>0.29166666666666669</v>
@@ -10319,7 +10447,7 @@
     </row>
     <row r="17" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B17" s="18">
         <v>0.29166666666666669</v>
@@ -10407,7 +10535,7 @@
     </row>
     <row r="18" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B18" s="18">
         <v>0.29166666666666669</v>
@@ -10495,7 +10623,7 @@
     </row>
     <row r="19" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="17">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B19" s="18">
         <v>0.29166666666666669</v>
@@ -10583,7 +10711,7 @@
     </row>
     <row r="20" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17">
-        <v>46221</v>
+        <v>46220</v>
       </c>
       <c r="B20" s="18">
         <v>0.29166666666666669</v>
@@ -10671,7 +10799,7 @@
     </row>
     <row r="21" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17">
-        <v>46222</v>
+        <v>46221</v>
       </c>
       <c r="B21" s="18">
         <v>0.29166666666666669</v>
@@ -10759,7 +10887,7 @@
     </row>
     <row r="22" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17">
-        <v>46223</v>
+        <v>46222</v>
       </c>
       <c r="B22" s="18">
         <v>0.29166666666666669</v>
@@ -10847,7 +10975,7 @@
     </row>
     <row r="23" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B23" s="18">
         <v>0.29166666666666669</v>
@@ -10935,7 +11063,7 @@
     </row>
     <row r="24" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B24" s="18">
         <v>0.29166666666666669</v>
@@ -11023,7 +11151,7 @@
     </row>
     <row r="25" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="17">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B25" s="18">
         <v>0.29166666666666669</v>
@@ -11111,7 +11239,7 @@
     </row>
     <row r="26" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B26" s="18">
         <v>0.29166666666666669</v>
@@ -11199,7 +11327,7 @@
     </row>
     <row r="27" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="17">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="B27" s="18">
         <v>0.29166666666666669</v>
@@ -11287,7 +11415,7 @@
     </row>
     <row r="28" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="17">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="B28" s="18">
         <v>0.29166666666666669</v>
@@ -11375,7 +11503,7 @@
     </row>
     <row r="29" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="17">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="B29" s="18">
         <v>0.29166666666666669</v>
@@ -11463,7 +11591,7 @@
     </row>
     <row r="30" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="17">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B30" s="18">
         <v>0.29166666666666669</v>
@@ -11551,7 +11679,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31" s="17">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B31" s="18">
         <v>0.29166666666666669</v>
@@ -11639,7 +11767,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32" s="17">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B32" s="18">
         <v>0.29166666666666669</v>
@@ -11727,7 +11855,7 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" s="17">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="13">
@@ -11812,37 +11940,62 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" s="17">
+        <v>46234</v>
+      </c>
+      <c r="B34" s="18"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44">
+        <f>Table113456[[#This Row],[Main Tank
+Opening Stock (Liters)]]-Table113456[[#This Row],[Main Tank
+Closing Stock (Liters)]]+Table113456[[#This Row],[Received (Liters)]]</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="13">
+        <f>VLOOKUP(D34,$T$2:$U$681,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="19">
+        <f>Table113456[[#This Row],[DG Parboiling 
+Run Hr Meter2]]-Table113456[[#This Row],[DG Milling Run Hr Meter]]</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13">
+        <f>Table113456[[#This Row],[DG Parboiling 
+Run Hr Meter4]]-Table113456[[#This Row],[DG Parboiling 
+Run Hr Meter]]</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="31"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="30">
+        <v>62</v>
+      </c>
+      <c r="U34" s="30">
+        <v>263.5</v>
+      </c>
+      <c r="V34" s="21"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>26</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>27</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <f>SUM(Table113456[Received (Liters)])</f>
         <v>37278</v>
-      </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="T34" s="30">
-        <v>62</v>
-      </c>
-      <c r="U34" s="30">
-        <v>263.5</v>
-      </c>
-      <c r="V34" s="21"/>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35">
-        <f>SUM(Table113456[Main Tank
-Consumption (Liters)])</f>
-        <v>34844</v>
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
@@ -11858,6 +12011,14 @@
       <c r="V35" s="21"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36">
+        <f>SUM(Table113456[Main Tank
+Consumption (Liters)])</f>
+        <v>34844</v>
+      </c>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21"/>
@@ -11872,12 +12033,6 @@
       <c r="V36" s="21"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
@@ -11892,7 +12047,9 @@
       <c r="V37" s="21"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A38" s="36"/>
+      <c r="A38" s="35" t="s">
+        <v>50</v>
+      </c>
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
       <c r="D38" s="36"/>
@@ -11918,6 +12075,7 @@
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
       <c r="T39" s="30">
         <v>72</v>
       </c>
@@ -11974,6 +12132,10 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A43" s="36"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
       <c r="G43" s="21"/>
@@ -11998,6 +12160,10 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
       <c r="T45" s="30">
         <v>84</v>
       </c>
@@ -22568,7 +22734,7 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
-    <mergeCell ref="A37:D42"/>
+    <mergeCell ref="A38:D43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -22625,7 +22791,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="7">
@@ -22656,7 +22822,7 @@
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>31</v>
@@ -22696,7 +22862,7 @@
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>31</v>
@@ -22736,7 +22902,7 @@
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>31</v>
@@ -22776,7 +22942,7 @@
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>31</v>
@@ -22816,7 +22982,7 @@
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>31</v>
@@ -22856,7 +23022,7 @@
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>31</v>
@@ -22896,7 +23062,7 @@
     </row>
     <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>31</v>
@@ -22936,7 +23102,7 @@
     </row>
     <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>31</v>
@@ -22976,7 +23142,7 @@
     </row>
     <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>31</v>
@@ -23016,7 +23182,7 @@
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>31</v>
@@ -23056,7 +23222,7 @@
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>31</v>
@@ -23096,7 +23262,7 @@
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>46215</v>
+        <v>46214</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>31</v>
@@ -23136,7 +23302,7 @@
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>46216</v>
+        <v>46215</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>31</v>
@@ -23176,7 +23342,7 @@
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>31</v>
@@ -23216,7 +23382,7 @@
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>31</v>
@@ -23256,7 +23422,7 @@
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>31</v>
@@ -23296,7 +23462,7 @@
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>31</v>
@@ -23336,7 +23502,7 @@
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>46221</v>
+        <v>46220</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>31</v>
@@ -23376,7 +23542,7 @@
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>46222</v>
+        <v>46221</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>31</v>
@@ -23416,7 +23582,7 @@
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>46223</v>
+        <v>46222</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>31</v>
@@ -23456,7 +23622,7 @@
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>31</v>
@@ -23496,7 +23662,7 @@
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>31</v>
@@ -23536,7 +23702,7 @@
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>31</v>
@@ -23576,7 +23742,7 @@
     </row>
     <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>31</v>
@@ -23616,7 +23782,7 @@
     </row>
     <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>31</v>
@@ -23656,7 +23822,7 @@
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>31</v>
@@ -23696,7 +23862,7 @@
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>31</v>
@@ -23736,7 +23902,7 @@
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
@@ -23776,7 +23942,7 @@
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>31</v>
@@ -23816,7 +23982,7 @@
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>31</v>
@@ -23856,7 +24022,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
